--- a/reviews/a-envoyer/gossip-beauty-center-2026-08-17.xlsx
+++ b/reviews/a-envoyer/gossip-beauty-center-2026-08-17.xlsx
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-17T07:09:38</t>
+          <t>2026-08-17T07:32:34</t>
         </is>
       </c>
     </row>
